--- a/src/src/main/webapp/portal/wo/woExport/APM_WorkOrderDetail_Template_en.xlsx
+++ b/src/src/main/webapp/portal/wo/woExport/APM_WorkOrderDetail_Template_en.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88301445-6940-4855-86B1-7448274D2BDC}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68AAF34F-C948-49DD-9F44-30F487551121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="4320" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WorkOrderDetail List" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Department</t>
   </si>
@@ -59,6 +59,10 @@
   </si>
   <si>
     <t>CloseStatus</t>
+  </si>
+  <si>
+    <t>ApprovalStatus</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -66,28 +70,28 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -136,15 +140,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -422,24 +426,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="27.3671875" customWidth="1"/>
-    <col min="2" max="2" width="20.3671875" customWidth="1"/>
-    <col min="3" max="3" width="25.3671875" customWidth="1"/>
-    <col min="4" max="4" width="32.47265625" customWidth="1"/>
-    <col min="5" max="5" width="20.26171875" customWidth="1"/>
-    <col min="7" max="7" width="13.62890625" customWidth="1"/>
-    <col min="8" max="8" width="14.89453125" customWidth="1"/>
-    <col min="9" max="9" width="24.47265625" customWidth="1"/>
-    <col min="10" max="10" width="14.26171875" customWidth="1"/>
-    <col min="11" max="11" width="16.26171875" customWidth="1"/>
-    <col min="12" max="12" width="11.26171875" customWidth="1"/>
-    <col min="13" max="13" width="12.62890625" customWidth="1"/>
+    <col min="1" max="1" width="27.375" customWidth="1"/>
+    <col min="2" max="2" width="20.375" customWidth="1"/>
+    <col min="3" max="3" width="25.375" customWidth="1"/>
+    <col min="4" max="4" width="32.5" customWidth="1"/>
+    <col min="5" max="5" width="20.25" customWidth="1"/>
+    <col min="7" max="7" width="13.625" customWidth="1"/>
+    <col min="8" max="8" width="14.875" customWidth="1"/>
+    <col min="9" max="9" width="24.5" customWidth="1"/>
+    <col min="10" max="10" width="14.25" customWidth="1"/>
+    <col min="11" max="11" width="15.25" customWidth="1"/>
+    <col min="12" max="12" width="16.25" customWidth="1"/>
+    <col min="13" max="13" width="11.25" customWidth="1"/>
+    <col min="14" max="14" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="27" customHeight="1">
+    <row r="1" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -471,12 +476,15 @@
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
     </row>

--- a/src/src/main/webapp/portal/wo/woExport/APM_WorkOrderDetail_Template_en.xlsx
+++ b/src/src/main/webapp/portal/wo/woExport/APM_WorkOrderDetail_Template_en.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68AAF34F-C948-49DD-9F44-30F487551121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C554056-4B2F-4506-A417-BB1DDD4AC94B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WorkOrderDetail List" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Department</t>
   </si>
@@ -63,6 +63,9 @@
   <si>
     <t>ApprovalStatus</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SerialNumber</t>
   </si>
 </sst>
 </file>
@@ -70,10 +73,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="164" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -132,18 +135,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -426,32 +426,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:O1"/>
+  <sheetFormatPr defaultRowHeight="14.1"/>
   <cols>
-    <col min="1" max="1" width="27.375" customWidth="1"/>
-    <col min="2" max="2" width="20.375" customWidth="1"/>
-    <col min="3" max="3" width="25.375" customWidth="1"/>
+    <col min="1" max="1" width="27.34765625" customWidth="1"/>
+    <col min="2" max="2" width="20.34765625" customWidth="1"/>
+    <col min="3" max="3" width="25.34765625" customWidth="1"/>
     <col min="4" max="4" width="32.5" customWidth="1"/>
     <col min="5" max="5" width="20.25" customWidth="1"/>
-    <col min="7" max="7" width="13.625" customWidth="1"/>
-    <col min="8" max="8" width="14.875" customWidth="1"/>
-    <col min="9" max="9" width="24.5" customWidth="1"/>
-    <col min="10" max="10" width="14.25" customWidth="1"/>
-    <col min="11" max="11" width="15.25" customWidth="1"/>
-    <col min="12" max="12" width="16.25" customWidth="1"/>
-    <col min="13" max="13" width="11.25" customWidth="1"/>
-    <col min="14" max="14" width="12.625" customWidth="1"/>
+    <col min="7" max="7" width="13.59765625" customWidth="1"/>
+    <col min="8" max="8" width="14.84765625" customWidth="1"/>
+    <col min="9" max="10" width="24.5" customWidth="1"/>
+    <col min="11" max="11" width="14.25" customWidth="1"/>
+    <col min="12" max="12" width="15.25" customWidth="1"/>
+    <col min="13" max="13" width="16.25" customWidth="1"/>
+    <col min="14" max="14" width="11.25" customWidth="1"/>
+    <col min="15" max="15" width="12.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" ht="27" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -463,28 +463,31 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
